--- a/tests/unit/bsee/analysis/financial-analysis-sme-code/scripts/leases.xlsx
+++ b/tests/unit/bsee/analysis/financial-analysis-sme-code/scripts/leases.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07f9c9cfd5dcd705/Roy/FDAS/Mktg/1-World Oil/2025 article/Economics/Testing2/V20/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="23" documentId="8_{F9554606-07CB-48CD-A820-9E00F634D39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09895552-4229-4394-90B0-123AB8CFB658}"/>
